--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>300</v>
+        <v>395</v>
       </c>
       <c r="D3">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G3">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Qwen3-Next-80B-A3B-Instruct/default/total_votes_file.xlsx
@@ -433,13 +433,13 @@
         <v>371</v>
       </c>
       <c r="D2">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H3">
         <v>426</v>
